--- a/artfynd/A 36595-2025 artfynd.xlsx
+++ b/artfynd/A 36595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127319887</v>
       </c>
       <c r="B2" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127320031</v>
       </c>
       <c r="B3" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36595-2025 artfynd.xlsx
+++ b/artfynd/A 36595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127319887</v>
       </c>
       <c r="B2" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127320031</v>
       </c>
       <c r="B3" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36595-2025 artfynd.xlsx
+++ b/artfynd/A 36595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127319887</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127320031</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36595-2025 artfynd.xlsx
+++ b/artfynd/A 36595-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127319887</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>127320031</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36595-2025 artfynd.xlsx
+++ b/artfynd/A 36595-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127319887</v>
+        <v>130935550</v>
       </c>
       <c r="B2" t="n">
-        <v>57832</v>
+        <v>58112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -708,21 +708,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>upprörd, varnande</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Källsberg A36595, Sm</t>
+          <t>Hässelåkravägen, Dalhem, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567304</v>
+        <v>567325</v>
       </c>
       <c r="R2" t="n">
-        <v>6433313</v>
+        <v>6433339</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,22 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:58</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +772,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Björn Stenberg</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127320031</v>
+        <v>127319887</v>
       </c>
       <c r="B3" t="n">
-        <v>57832</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,14 +824,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Källsberg A36595, Källsberg A36595, Sm</t>
+          <t>Källsberg A36595, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567262</v>
+        <v>567304</v>
       </c>
       <c r="R3" t="n">
-        <v>6433360</v>
+        <v>6433313</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,6 +897,231 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127320031</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Källsberg A36595, Källsberg A36595, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>567262</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6433360</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Björn Stenberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130935544</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hässelåkravägen, Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>567325</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6433339</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
